--- a/data/migration_metarecycling_template.xlsx
+++ b/data/migration_metarecycling_template.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
     <row r="1" ht="45" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOTAS: OPCIONAL: las 7 default ya vienen con la org. Solo agregar extras aqui. tipo_comportamiento: proveedor_material | proveedor_servicios | cliente | inversionista | generico | provision | pasivo.</t>
+          <t>NOTAS: OPCIONAL: las 7 default ya vienen con la org (Pasivo, Inversionista, etc). Solo agregar extras aqui. tipo_comportamiento: proveedor_material | proveedor_servicios | cliente | inversionista | generico | provision | pasivo. Convencion: creditos bancarios/leasings van como 'Obligaciones Financieras' (inversionista) — el reporte los distingue por nombre.</t>
         </is>
       </c>
     </row>
@@ -669,6 +669,19 @@
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Obligaciones Financieras</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>inversionista</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -899,7 +912,7 @@
     <row r="1" ht="45" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOTAS: categorias: CSV de nombres (ej: 'Proveedor Material,Cliente' para alguien que es ambos). saldo_inicial: positivo = nos debe, negativo = le debemos. Categorias internas: Pasivo y Provision son aceptadas.</t>
+          <t>NOTAS: categorias: CSV de nombres (ej: 'Proveedor Material,Cliente' para alguien que es ambos). saldo_inicial: positivo = nos debe, negativo = le debemos. Creditos bancarios/leasings: usar 'Obligaciones Financieras' (debe estar declarada en hoja CategoriaTerceros con tipo_comportamiento=inversionista). Categorias internas Pasivo y Provision tambien son aceptadas pero quedan en seccion 'Pasivos' del balance.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1046,7 @@
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Pasivo</t>
+          <t>Obligaciones Financieras</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
